--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/66.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/66.xlsx
@@ -426,13 +426,13 @@
         <v>-7.273881376489707</v>
       </c>
       <c r="E2">
-        <v>-7.588977315351856</v>
+        <v>-9.969632328976223</v>
       </c>
       <c r="F2">
-        <v>-0.547579993357079</v>
+        <v>-0.6438147480099087</v>
       </c>
       <c r="G2">
-        <v>-5.454406303897462</v>
+        <v>-7.924542706063038</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.135142748754783</v>
       </c>
       <c r="E3">
-        <v>-7.734966260411133</v>
+        <v>-10.48507229747728</v>
       </c>
       <c r="F3">
-        <v>-0.2795584067116877</v>
+        <v>-0.4041771704214425</v>
       </c>
       <c r="G3">
-        <v>-6.261796805700666</v>
+        <v>-7.553708889079275</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.93191098982008</v>
       </c>
       <c r="E4">
-        <v>-8.374241879125941</v>
+        <v>-11.71530924571906</v>
       </c>
       <c r="F4">
-        <v>-0.331710761657139</v>
+        <v>-0.05695537639439056</v>
       </c>
       <c r="G4">
-        <v>-6.327811702255135</v>
+        <v>-8.543157969108268</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.691757304128886</v>
       </c>
       <c r="E5">
-        <v>-9.827728067471865</v>
+        <v>-11.45515294245241</v>
       </c>
       <c r="F5">
-        <v>0.04639091241147296</v>
+        <v>-0.6680146733152935</v>
       </c>
       <c r="G5">
-        <v>-5.671882387635898</v>
+        <v>-7.594602753374634</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.422141662087311</v>
       </c>
       <c r="E6">
-        <v>-10.29670136418022</v>
+        <v>-11.13128100989783</v>
       </c>
       <c r="F6">
-        <v>0.05990324148593849</v>
+        <v>-0.3587553006237372</v>
       </c>
       <c r="G6">
-        <v>-5.774259781512132</v>
+        <v>-7.187367064410391</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.137404248376924</v>
       </c>
       <c r="E7">
-        <v>-10.30152418899838</v>
+        <v>-12.2130247669541</v>
       </c>
       <c r="F7">
-        <v>0.05750843132444512</v>
+        <v>0.2811253833427689</v>
       </c>
       <c r="G7">
-        <v>-6.321826754130707</v>
+        <v>-6.22123762600437</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.850140404906271</v>
       </c>
       <c r="E8">
-        <v>-11.16530796359147</v>
+        <v>-12.84872741967685</v>
       </c>
       <c r="F8">
-        <v>0.2626643874039791</v>
+        <v>0.03175531713881129</v>
       </c>
       <c r="G8">
-        <v>-5.253867885848878</v>
+        <v>-6.847573603378974</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.57771237898286</v>
       </c>
       <c r="E9">
-        <v>-12.76157693739924</v>
+        <v>-14.49899844602609</v>
       </c>
       <c r="F9">
-        <v>-0.01143575924315493</v>
+        <v>0.1817287503134534</v>
       </c>
       <c r="G9">
-        <v>-5.073285857324839</v>
+        <v>-5.703775861193701</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.333561191952998</v>
       </c>
       <c r="E10">
-        <v>-12.28584715747144</v>
+        <v>-15.55504764156283</v>
       </c>
       <c r="F10">
-        <v>0.1389071257931357</v>
+        <v>0.5386167635637727</v>
       </c>
       <c r="G10">
-        <v>-4.488962640797364</v>
+        <v>-6.781916359974486</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.125664680754837</v>
       </c>
       <c r="E11">
-        <v>-12.93993994313935</v>
+        <v>-15.14637097626662</v>
       </c>
       <c r="F11">
-        <v>0.09762295117241399</v>
+        <v>0.7758843820128296</v>
       </c>
       <c r="G11">
-        <v>-3.774092743305823</v>
+        <v>-7.023355204761547</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.961258673458825</v>
       </c>
       <c r="E12">
-        <v>-14.31451747190162</v>
+        <v>-17.20279177941579</v>
       </c>
       <c r="F12">
-        <v>0.09286895064774763</v>
+        <v>0.3430682126219075</v>
       </c>
       <c r="G12">
-        <v>-3.497997636407906</v>
+        <v>-5.755691348707234</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.845372992252447</v>
       </c>
       <c r="E13">
-        <v>-15.17404448092749</v>
+        <v>-17.00580768855614</v>
       </c>
       <c r="F13">
-        <v>0.576536109794323</v>
+        <v>0.3801881843087561</v>
       </c>
       <c r="G13">
-        <v>-3.729477973762052</v>
+        <v>-3.952551821480902</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.787854792304581</v>
       </c>
       <c r="E14">
-        <v>-15.8649220609597</v>
+        <v>-18.29731941859571</v>
       </c>
       <c r="F14">
-        <v>0.4430413893635715</v>
+        <v>0.2519834181122823</v>
       </c>
       <c r="G14">
-        <v>-2.754886264954224</v>
+        <v>-3.459128285814724</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.78943714618387</v>
       </c>
       <c r="E15">
-        <v>-15.96492435247109</v>
+        <v>-19.40247991474564</v>
       </c>
       <c r="F15">
-        <v>0.7815040264734214</v>
+        <v>0.5310529408088105</v>
       </c>
       <c r="G15">
-        <v>-2.973441870585718</v>
+        <v>-2.741420131674263</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.842345984854687</v>
       </c>
       <c r="E16">
-        <v>-17.58480478975485</v>
+        <v>-19.30754951412285</v>
       </c>
       <c r="F16">
-        <v>0.5512535082934793</v>
+        <v>0.7264076537784208</v>
       </c>
       <c r="G16">
-        <v>-2.391189104862252</v>
+        <v>-3.803453113819734</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.941847279406237</v>
       </c>
       <c r="E17">
-        <v>-17.29598777449365</v>
+        <v>-20.94976891368645</v>
       </c>
       <c r="F17">
-        <v>0.4502440439309131</v>
+        <v>0.7598952344039935</v>
       </c>
       <c r="G17">
-        <v>-2.155403804822115</v>
+        <v>-2.791160169293885</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.081544059889691</v>
       </c>
       <c r="E18">
-        <v>-19.42362335988745</v>
+        <v>-20.70337917140311</v>
       </c>
       <c r="F18">
-        <v>1.061300027382205</v>
+        <v>1.51845777290439</v>
       </c>
       <c r="G18">
-        <v>-1.484912428922063</v>
+        <v>-3.133660638111843</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.255994594687723</v>
       </c>
       <c r="E19">
-        <v>-19.65623748423945</v>
+        <v>-20.27558328884651</v>
       </c>
       <c r="F19">
-        <v>0.9483140271099635</v>
+        <v>0.686462120880623</v>
       </c>
       <c r="G19">
-        <v>-1.292255505059266</v>
+        <v>-3.520227912473144</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.455063224237399</v>
       </c>
       <c r="E20">
-        <v>-20.71856767322484</v>
+        <v>-23.41260667360202</v>
       </c>
       <c r="F20">
-        <v>1.128232113528405</v>
+        <v>1.399709648978276</v>
       </c>
       <c r="G20">
-        <v>-0.6974586293140442</v>
+        <v>-1.750412471404532</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.669621239679549</v>
       </c>
       <c r="E21">
-        <v>-19.59914248395075</v>
+        <v>-23.91807947081219</v>
       </c>
       <c r="F21">
-        <v>1.312901715369304</v>
+        <v>2.171411751221878</v>
       </c>
       <c r="G21">
-        <v>-1.15165844245862</v>
+        <v>-2.039097625426038</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.894896651326057</v>
       </c>
       <c r="E22">
-        <v>-21.41045963143477</v>
+        <v>-23.02806677476668</v>
       </c>
       <c r="F22">
-        <v>1.444009080945188</v>
+        <v>1.219930728283505</v>
       </c>
       <c r="G22">
-        <v>-0.4369001065000988</v>
+        <v>-0.9767365211246217</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.130921287830895</v>
       </c>
       <c r="E23">
-        <v>-22.24964926369219</v>
+        <v>-24.13949015046922</v>
       </c>
       <c r="F23">
-        <v>1.138565168510926</v>
+        <v>1.899781796169892</v>
       </c>
       <c r="G23">
-        <v>0.1352694653711924</v>
+        <v>-3.094436915590241</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.376355999373884</v>
       </c>
       <c r="E24">
-        <v>-22.28981229966622</v>
+        <v>-23.88965876794005</v>
       </c>
       <c r="F24">
-        <v>1.57675827071342</v>
+        <v>1.542419128397769</v>
       </c>
       <c r="G24">
-        <v>-0.706436051500685</v>
+        <v>-1.857222795607576</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.624003430049095</v>
       </c>
       <c r="E25">
-        <v>-22.24681443896339</v>
+        <v>-23.8551472675276</v>
       </c>
       <c r="F25">
-        <v>1.707174777875368</v>
+        <v>2.146764507518982</v>
       </c>
       <c r="G25">
-        <v>0.5688402385715388</v>
+        <v>-2.059779164915217</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.872333405159894</v>
       </c>
       <c r="E26">
-        <v>-22.46935270864833</v>
+        <v>-25.47384577309536</v>
       </c>
       <c r="F26">
-        <v>1.10881683834159</v>
+        <v>2.102518091065849</v>
       </c>
       <c r="G26">
-        <v>-0.3072951361235919</v>
+        <v>-0.6296193735725247</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.118399463907681</v>
       </c>
       <c r="E27">
-        <v>-21.7435153092769</v>
+        <v>-24.55317077954391</v>
       </c>
       <c r="F27">
-        <v>1.511913670422274</v>
+        <v>2.478131349456451</v>
       </c>
       <c r="G27">
-        <v>0.1014072588777229</v>
+        <v>-1.933832756577492</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.36169720345687</v>
       </c>
       <c r="E28">
-        <v>-22.59212869594429</v>
+        <v>-24.96257652915537</v>
       </c>
       <c r="F28">
-        <v>1.262157585008612</v>
+        <v>2.179834590973543</v>
       </c>
       <c r="G28">
-        <v>0.4702067184946306</v>
+        <v>-1.526757847469661</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.597379109281722</v>
       </c>
       <c r="E29">
-        <v>-22.01890539910536</v>
+        <v>-24.33480323442004</v>
       </c>
       <c r="F29">
-        <v>1.378319545903187</v>
+        <v>2.398629616340171</v>
       </c>
       <c r="G29">
-        <v>0.4003856049312066</v>
+        <v>-1.624886059426415</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.817545115412484</v>
       </c>
       <c r="E30">
-        <v>-20.83252672162786</v>
+        <v>-24.63825627767403</v>
       </c>
       <c r="F30">
-        <v>1.573857328068816</v>
+        <v>2.134678627112137</v>
       </c>
       <c r="G30">
-        <v>-0.4958144395999287</v>
+        <v>-1.508159883670728</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.019647423901365</v>
       </c>
       <c r="E31">
-        <v>-21.94507768735831</v>
+        <v>-23.88331890432931</v>
       </c>
       <c r="F31">
-        <v>1.658163592121333</v>
+        <v>1.139637075930148</v>
       </c>
       <c r="G31">
-        <v>0.2789475950161576</v>
+        <v>-2.329446358778181</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.202267446609905</v>
       </c>
       <c r="E32">
-        <v>-21.20277022802098</v>
+        <v>-22.88398884573864</v>
       </c>
       <c r="F32">
-        <v>1.38507571044042</v>
+        <v>1.823757549410565</v>
       </c>
       <c r="G32">
-        <v>-0.4177705848085361</v>
+        <v>-1.189487645817458</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.363209367709914</v>
       </c>
       <c r="E33">
-        <v>-20.84071873110774</v>
+        <v>-23.18920799385562</v>
       </c>
       <c r="F33">
-        <v>1.618706795991186</v>
+        <v>2.06281775491928</v>
       </c>
       <c r="G33">
-        <v>-1.185760178125928</v>
+        <v>-1.778657226588232</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.494845747566712</v>
       </c>
       <c r="E34">
-        <v>-19.94211551986968</v>
+        <v>-22.62016447852577</v>
       </c>
       <c r="F34">
-        <v>1.394658264556004</v>
+        <v>1.498832092397264</v>
       </c>
       <c r="G34">
-        <v>-1.275606586866644</v>
+        <v>-2.484320016383972</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.593565030097281</v>
       </c>
       <c r="E35">
-        <v>-19.40625666206804</v>
+        <v>-22.63906632903379</v>
       </c>
       <c r="F35">
-        <v>1.447092264418407</v>
+        <v>2.065052690172033</v>
       </c>
       <c r="G35">
-        <v>-1.55625274806751</v>
+        <v>-4.025828061346421</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.655964268210314</v>
       </c>
       <c r="E36">
-        <v>-18.4383542130906</v>
+        <v>-23.04148917172542</v>
       </c>
       <c r="F36">
-        <v>1.254041241195983</v>
+        <v>1.680950322637542</v>
       </c>
       <c r="G36">
-        <v>-1.755488521156993</v>
+        <v>-4.044219308187109</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.685336608702059</v>
       </c>
       <c r="E37">
-        <v>-18.4208199617329</v>
+        <v>-21.72180127641012</v>
       </c>
       <c r="F37">
-        <v>1.574672441593171</v>
+        <v>2.245005568021392</v>
       </c>
       <c r="G37">
-        <v>-1.727565325686118</v>
+        <v>-2.446855028618232</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.680908700682325</v>
       </c>
       <c r="E38">
-        <v>-18.00243877663824</v>
+        <v>-20.76513849991972</v>
       </c>
       <c r="F38">
-        <v>1.657833901895018</v>
+        <v>1.823790684106677</v>
       </c>
       <c r="G38">
-        <v>-2.966981145335171</v>
+        <v>-4.771331443316939</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.63888624694262</v>
       </c>
       <c r="E39">
-        <v>-17.95307388148063</v>
+        <v>-20.24357150608629</v>
       </c>
       <c r="F39">
-        <v>2.010948701625586</v>
+        <v>2.462408936151317</v>
       </c>
       <c r="G39">
-        <v>-3.04362719974224</v>
+        <v>-4.769057556776244</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.56304946046693</v>
       </c>
       <c r="E40">
-        <v>-16.01698821813727</v>
+        <v>-19.82968709568124</v>
       </c>
       <c r="F40">
-        <v>1.953799634506448</v>
+        <v>2.291231782567216</v>
       </c>
       <c r="G40">
-        <v>-2.991406558623677</v>
+        <v>-4.455234964387832</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.459062176896893</v>
       </c>
       <c r="E41">
-        <v>-16.87419664847122</v>
+        <v>-19.69364720801682</v>
       </c>
       <c r="F41">
-        <v>2.031180747071561</v>
+        <v>2.681187394169888</v>
       </c>
       <c r="G41">
-        <v>-4.141067843735679</v>
+        <v>-4.324429066920569</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.335057064722132</v>
       </c>
       <c r="E42">
-        <v>-15.35578572827732</v>
+        <v>-20.50906235173398</v>
       </c>
       <c r="F42">
-        <v>2.006613026639334</v>
+        <v>1.926261388567782</v>
       </c>
       <c r="G42">
-        <v>-3.933445268340255</v>
+        <v>-4.455464649896993</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.194156316564975</v>
       </c>
       <c r="E43">
-        <v>-13.60349723948329</v>
+        <v>-17.98694233858399</v>
       </c>
       <c r="F43">
-        <v>2.194665680953266</v>
+        <v>2.033114156589695</v>
       </c>
       <c r="G43">
-        <v>-3.671968003489665</v>
+        <v>-5.526662083857993</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.039962230734194</v>
       </c>
       <c r="E44">
-        <v>-14.10032970828683</v>
+        <v>-19.59454155435895</v>
       </c>
       <c r="F44">
-        <v>2.350521351055187</v>
+        <v>2.212909644632522</v>
       </c>
       <c r="G44">
-        <v>-4.252015788325183</v>
+        <v>-4.5206592410616</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.875826008202812</v>
       </c>
       <c r="E45">
-        <v>-13.56735548842807</v>
+        <v>-17.99542869887437</v>
       </c>
       <c r="F45">
-        <v>2.538002431861188</v>
+        <v>1.951244949436215</v>
       </c>
       <c r="G45">
-        <v>-4.345527321547798</v>
+        <v>-6.237551859597929</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.710901488053651</v>
       </c>
       <c r="E46">
-        <v>-13.5986653577171</v>
+        <v>-14.42492619668263</v>
       </c>
       <c r="F46">
-        <v>2.822462141247733</v>
+        <v>2.875920003219996</v>
       </c>
       <c r="G46">
-        <v>-4.386096344908773</v>
+        <v>-6.040672003588127</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.548511943054764</v>
       </c>
       <c r="E47">
-        <v>-12.21806495852463</v>
+        <v>-16.39771967033216</v>
       </c>
       <c r="F47">
-        <v>2.315166630303704</v>
+        <v>1.87795265837132</v>
       </c>
       <c r="G47">
-        <v>-3.867643651187151</v>
+        <v>-5.164618659431983</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.385854938081893</v>
       </c>
       <c r="E48">
-        <v>-11.25461399949673</v>
+        <v>-14.66743503674139</v>
       </c>
       <c r="F48">
-        <v>2.641101038813615</v>
+        <v>2.5812365833481</v>
       </c>
       <c r="G48">
-        <v>-5.035407435642609</v>
+        <v>-4.561339825955596</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.223209264253168</v>
       </c>
       <c r="E49">
-        <v>-11.59930332706457</v>
+        <v>-13.811145886631</v>
       </c>
       <c r="F49">
-        <v>2.193613654351711</v>
+        <v>2.024890125014702</v>
       </c>
       <c r="G49">
-        <v>-4.855517744867612</v>
+        <v>-5.367709867853813</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.059825923728989</v>
       </c>
       <c r="E50">
-        <v>-10.27541300787016</v>
+        <v>-14.27742021283078</v>
       </c>
       <c r="F50">
-        <v>2.56926170417323</v>
+        <v>2.620063820252119</v>
       </c>
       <c r="G50">
-        <v>-4.836588377691175</v>
+        <v>-5.229846062812184</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.898689516432102</v>
       </c>
       <c r="E51">
-        <v>-8.828144414336764</v>
+        <v>-13.41291188239647</v>
       </c>
       <c r="F51">
-        <v>2.505358129251666</v>
+        <v>2.403316519105211</v>
       </c>
       <c r="G51">
-        <v>-5.382869111458448</v>
+        <v>-7.398671170395511</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.73671967626461</v>
       </c>
       <c r="E52">
-        <v>-8.58340303659222</v>
+        <v>-13.78305123388742</v>
       </c>
       <c r="F52">
-        <v>2.680059157767276</v>
+        <v>2.369037019242562</v>
       </c>
       <c r="G52">
-        <v>-4.868157010314593</v>
+        <v>-5.61791941786927</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.569292127225364</v>
       </c>
       <c r="E53">
-        <v>-8.322585576120446</v>
+        <v>-10.76586032832288</v>
       </c>
       <c r="F53">
-        <v>2.583726655760915</v>
+        <v>2.296750366204666</v>
       </c>
       <c r="G53">
-        <v>-5.164713814857206</v>
+        <v>-5.814884585639617</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.392795260326166</v>
       </c>
       <c r="E54">
-        <v>-7.473840863706837</v>
+        <v>-10.73612183951451</v>
       </c>
       <c r="F54">
-        <v>2.490285155990326</v>
+        <v>2.665802954765096</v>
       </c>
       <c r="G54">
-        <v>-5.694417817306164</v>
+        <v>-6.435717954459033</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.208371164422405</v>
       </c>
       <c r="E55">
-        <v>-7.286484308587491</v>
+        <v>-10.29288386059175</v>
       </c>
       <c r="F55">
-        <v>2.30522622147011</v>
+        <v>2.435945911101484</v>
       </c>
       <c r="G55">
-        <v>-5.260591108824181</v>
+        <v>-5.657819072032118</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.015649659169268</v>
       </c>
       <c r="E56">
-        <v>-6.486058413835725</v>
+        <v>-10.93725401256519</v>
       </c>
       <c r="F56">
-        <v>2.309049965401433</v>
+        <v>1.900656552147249</v>
       </c>
       <c r="G56">
-        <v>-6.023137155574455</v>
+        <v>-6.822209760724466</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.811516302169418</v>
       </c>
       <c r="E57">
-        <v>-4.982351448744736</v>
+        <v>-10.35529528936546</v>
       </c>
       <c r="F57">
-        <v>2.514176928621869</v>
+        <v>2.290453117208584</v>
       </c>
       <c r="G57">
-        <v>-6.154520548036181</v>
+        <v>-6.874551807040729</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.595812396197841</v>
       </c>
       <c r="E58">
-        <v>-5.339937870286419</v>
+        <v>-9.026804040579256</v>
       </c>
       <c r="F58">
-        <v>2.029106515094951</v>
+        <v>2.294394489311104</v>
       </c>
       <c r="G58">
-        <v>-5.362801160400884</v>
+        <v>-6.0810146226615</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.368324068169975</v>
       </c>
       <c r="E59">
-        <v>-6.187496122510018</v>
+        <v>-9.437052086356136</v>
       </c>
       <c r="F59">
-        <v>2.343268166076275</v>
+        <v>2.386527168585271</v>
       </c>
       <c r="G59">
-        <v>-6.104836291183068</v>
+        <v>-5.907444564609993</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.135718621566555</v>
       </c>
       <c r="E60">
-        <v>-5.441887405621102</v>
+        <v>-8.676639787936145</v>
       </c>
       <c r="F60">
-        <v>1.800311438441728</v>
+        <v>1.776880238086141</v>
       </c>
       <c r="G60">
-        <v>-6.397193132129592</v>
+        <v>-6.094208414552027</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.899961501721738</v>
       </c>
       <c r="E61">
-        <v>-3.872137175602249</v>
+        <v>-6.621138265010524</v>
       </c>
       <c r="F61">
-        <v>1.810228652988043</v>
+        <v>1.984986010487044</v>
       </c>
       <c r="G61">
-        <v>-5.816905818120235</v>
+        <v>-6.810502362200368</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.661793265229814</v>
       </c>
       <c r="E62">
-        <v>-3.438132755181129</v>
+        <v>-7.319229704136955</v>
       </c>
       <c r="F62">
-        <v>2.060715358450975</v>
+        <v>1.913847474669428</v>
       </c>
       <c r="G62">
-        <v>-5.643230760978827</v>
+        <v>-6.55043274139878</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.423500866345485</v>
       </c>
       <c r="E63">
-        <v>-4.548306272057548</v>
+        <v>-7.515448482889312</v>
       </c>
       <c r="F63">
-        <v>2.307583755098478</v>
+        <v>2.339616722564735</v>
       </c>
       <c r="G63">
-        <v>-5.905193646620214</v>
+        <v>-7.259199566789754</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.189464387261116</v>
       </c>
       <c r="E64">
-        <v>-3.478150879986912</v>
+        <v>-6.396775020300495</v>
       </c>
       <c r="F64">
-        <v>1.851617201901518</v>
+        <v>2.313929049403922</v>
       </c>
       <c r="G64">
-        <v>-5.301560441215408</v>
+        <v>-6.702235175624931</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.963768816035147</v>
       </c>
       <c r="E65">
-        <v>-3.076266925702198</v>
+        <v>-8.595140841220102</v>
       </c>
       <c r="F65">
-        <v>1.9591707687462</v>
+        <v>2.352274176479511</v>
       </c>
       <c r="G65">
-        <v>-6.043772757961802</v>
+        <v>-6.126646570888697</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.746438364317582</v>
       </c>
       <c r="E66">
-        <v>-2.476284875951945</v>
+        <v>-5.88145279212364</v>
       </c>
       <c r="F66">
-        <v>1.864559614202858</v>
+        <v>1.743084504786727</v>
       </c>
       <c r="G66">
-        <v>-5.02104224765536</v>
+        <v>-6.693943528744214</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.537351539817176</v>
       </c>
       <c r="E67">
-        <v>-2.84239841405007</v>
+        <v>-7.857601865012853</v>
       </c>
       <c r="F67">
-        <v>1.691997430321276</v>
+        <v>1.931907540785263</v>
       </c>
       <c r="G67">
-        <v>-5.721907891531192</v>
+        <v>-7.134536116081772</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.335021809696612</v>
       </c>
       <c r="E68">
-        <v>-3.000763678572311</v>
+        <v>-7.640076616054408</v>
       </c>
       <c r="F68">
-        <v>1.676518557032564</v>
+        <v>2.162085991001161</v>
       </c>
       <c r="G68">
-        <v>-5.289872730020665</v>
+        <v>-6.004552316661759</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.143225315282052</v>
       </c>
       <c r="E69">
-        <v>-3.257596081917335</v>
+        <v>-6.959383574065446</v>
       </c>
       <c r="F69">
-        <v>1.669406194512127</v>
+        <v>1.853108263226557</v>
       </c>
       <c r="G69">
-        <v>-4.798585269589687</v>
+        <v>-7.110806321763867</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.961961528179672</v>
       </c>
       <c r="E70">
-        <v>-3.217985519772242</v>
+        <v>-6.016609627356569</v>
       </c>
       <c r="F70">
-        <v>1.783071456054665</v>
+        <v>2.012227700895509</v>
       </c>
       <c r="G70">
-        <v>-4.584380563746016</v>
+        <v>-5.30190496947915</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.789165983767847</v>
       </c>
       <c r="E71">
-        <v>-3.107884731223753</v>
+        <v>-6.396648223028281</v>
       </c>
       <c r="F71">
-        <v>1.247228747675359</v>
+        <v>1.936948984798701</v>
       </c>
       <c r="G71">
-        <v>-3.903454903286931</v>
+        <v>-5.919401335972609</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.624623833242418</v>
       </c>
       <c r="E72">
-        <v>-2.574371622958085</v>
+        <v>-6.593664013205988</v>
       </c>
       <c r="F72">
-        <v>1.268955167915985</v>
+        <v>1.705256278970485</v>
       </c>
       <c r="G72">
-        <v>-4.115205255404136</v>
+        <v>-6.472969662823409</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.469659250805635</v>
       </c>
       <c r="E73">
-        <v>-4.069433731168431</v>
+        <v>-6.764713533423713</v>
       </c>
       <c r="F73">
-        <v>1.466966455146373</v>
+        <v>1.952654830755779</v>
       </c>
       <c r="G73">
-        <v>-3.280984204909352</v>
+        <v>-5.847152118455196</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.328899481996084</v>
       </c>
       <c r="E74">
-        <v>-2.379873664328643</v>
+        <v>-6.420612907476873</v>
       </c>
       <c r="F74">
-        <v>1.389505819310591</v>
+        <v>1.643889165036291</v>
       </c>
       <c r="G74">
-        <v>-3.49336783278753</v>
+        <v>-5.73952805130541</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.205284169056426</v>
       </c>
       <c r="E75">
-        <v>-3.052596592064106</v>
+        <v>-7.376922462994676</v>
       </c>
       <c r="F75">
-        <v>1.053959035458596</v>
+        <v>1.090791563656673</v>
       </c>
       <c r="G75">
-        <v>-3.178304938649648</v>
+        <v>-6.076785128071376</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.102088672210933</v>
       </c>
       <c r="E76">
-        <v>-3.221001483461351</v>
+        <v>-6.783909734742227</v>
       </c>
       <c r="F76">
-        <v>0.8160452904353552</v>
+        <v>1.623375474673365</v>
       </c>
       <c r="G76">
-        <v>-3.114931425450533</v>
+        <v>-5.974424140302938</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.024623159675933</v>
       </c>
       <c r="E77">
-        <v>-4.236629520005628</v>
+        <v>-8.271825910968468</v>
       </c>
       <c r="F77">
-        <v>0.7114142037877497</v>
+        <v>0.8926527078462535</v>
       </c>
       <c r="G77">
-        <v>-3.453989892852634</v>
+        <v>-5.161567123381698</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.98146512635129</v>
       </c>
       <c r="E78">
-        <v>-4.457442441093642</v>
+        <v>-8.046031668472017</v>
       </c>
       <c r="F78">
-        <v>1.120132337063831</v>
+        <v>1.257247023044817</v>
       </c>
       <c r="G78">
-        <v>-3.531003444074361</v>
+        <v>-5.252893363045724</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.980432001914864</v>
       </c>
       <c r="E79">
-        <v>-5.303438369784596</v>
+        <v>-8.943063499229416</v>
       </c>
       <c r="F79">
-        <v>0.7174430617453245</v>
+        <v>1.627132949212463</v>
       </c>
       <c r="G79">
-        <v>-1.166046598996785</v>
+        <v>-5.247666377101528</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.025457117012532</v>
       </c>
       <c r="E80">
-        <v>-5.063922851044903</v>
+        <v>-9.205506681869943</v>
       </c>
       <c r="F80">
-        <v>0.7263678921430864</v>
+        <v>0.8664779546525947</v>
       </c>
       <c r="G80">
-        <v>-1.768688875490639</v>
+        <v>-4.282373650193166</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.122588297494152</v>
       </c>
       <c r="E81">
-        <v>-5.775300832909839</v>
+        <v>-9.858711886632346</v>
       </c>
       <c r="F81">
-        <v>0.4253333793939264</v>
+        <v>1.624180647788886</v>
       </c>
       <c r="G81">
-        <v>-0.4918047868542872</v>
+        <v>-4.605567411355351</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.277133565971121</v>
       </c>
       <c r="E82">
-        <v>-7.096519352439727</v>
+        <v>-9.964560438087632</v>
       </c>
       <c r="F82">
-        <v>0.1263407922926673</v>
+        <v>1.051361275283416</v>
       </c>
       <c r="G82">
-        <v>-1.2738544145539</v>
+        <v>-3.497699045245997</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.494864683057796</v>
       </c>
       <c r="E83">
-        <v>-6.973023337776548</v>
+        <v>-10.5432405461058</v>
       </c>
       <c r="F83">
-        <v>0.4853527395637646</v>
+        <v>0.9473961960276617</v>
       </c>
       <c r="G83">
-        <v>-0.3668329013197164</v>
+        <v>-4.917821579838348</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.777052494363831</v>
       </c>
       <c r="E84">
-        <v>-8.93782405480254</v>
+        <v>-12.93750815259723</v>
       </c>
       <c r="F84">
-        <v>0.5501526080151588</v>
+        <v>1.018395566121607</v>
       </c>
       <c r="G84">
-        <v>-0.01022317979614574</v>
+        <v>-3.279297657027797</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.119163103492535</v>
       </c>
       <c r="E85">
-        <v>-9.965728784381612</v>
+        <v>-11.93520741505753</v>
       </c>
       <c r="F85">
-        <v>0.3595626643464512</v>
+        <v>1.11939509007534</v>
       </c>
       <c r="G85">
-        <v>-0.04059088532880658</v>
+        <v>-2.906557450317997</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.522076172642608</v>
       </c>
       <c r="E86">
-        <v>-10.03827493798449</v>
+        <v>-13.69004090624387</v>
       </c>
       <c r="F86">
-        <v>-0.06339924642076791</v>
+        <v>0.1503940965677565</v>
       </c>
       <c r="G86">
-        <v>-0.6931569478496122</v>
+        <v>-3.280262336166274</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.984226814202745</v>
       </c>
       <c r="E87">
-        <v>-11.22249353336033</v>
+        <v>-15.38963154301065</v>
       </c>
       <c r="F87">
-        <v>0.0006749721857738449</v>
+        <v>0.9970270005989912</v>
       </c>
       <c r="G87">
-        <v>-0.1038298684439846</v>
+        <v>-2.553104263934611</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.502480477464954</v>
       </c>
       <c r="E88">
-        <v>-12.48879072012519</v>
+        <v>-15.63648318964277</v>
       </c>
       <c r="F88">
-        <v>-0.0508544504727722</v>
+        <v>0.7784755152487864</v>
       </c>
       <c r="G88">
-        <v>0.5696080444164489</v>
+        <v>-3.698910113714266</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.067260554522774</v>
       </c>
       <c r="E89">
-        <v>-14.80184467376306</v>
+        <v>-17.01131884142348</v>
       </c>
       <c r="F89">
-        <v>-0.52241419166003</v>
+        <v>0.1935959417259591</v>
       </c>
       <c r="G89">
-        <v>-0.3002962905372964</v>
+        <v>-2.786208805960683</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.670740292065513</v>
       </c>
       <c r="E90">
-        <v>-15.72761872904714</v>
+        <v>-20.27250392652129</v>
       </c>
       <c r="F90">
-        <v>-1.138917519152131</v>
+        <v>-0.1302103909261592</v>
       </c>
       <c r="G90">
-        <v>-0.3816148044450148</v>
+        <v>-3.072160702423171</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.308183801426207</v>
       </c>
       <c r="E91">
-        <v>-16.85313924433555</v>
+        <v>-20.07293407700326</v>
       </c>
       <c r="F91">
-        <v>-0.7596917505179204</v>
+        <v>-0.1207736294734673</v>
       </c>
       <c r="G91">
-        <v>0.7632230849746032</v>
+        <v>-2.228827699657809</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.974253379267325</v>
       </c>
       <c r="E92">
-        <v>-19.87567374922914</v>
+        <v>-22.02380973645566</v>
       </c>
       <c r="F92">
-        <v>-1.017076271343963</v>
+        <v>-0.1331842299022095</v>
       </c>
       <c r="G92">
-        <v>0.03087083901433988</v>
+        <v>-2.68464843625275</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.661240357629246</v>
       </c>
       <c r="E93">
-        <v>-21.68032951144788</v>
+        <v>-23.000506481956</v>
       </c>
       <c r="F93">
-        <v>-1.303170349616231</v>
+        <v>-0.05851602058126483</v>
       </c>
       <c r="G93">
-        <v>0.5511774229170479</v>
+        <v>-3.717478546519164</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.351198616545398</v>
       </c>
       <c r="E94">
-        <v>-22.63454691197413</v>
+        <v>-26.07615093001154</v>
       </c>
       <c r="F94">
-        <v>-1.525447831544228</v>
+        <v>-0.9258912443785992</v>
       </c>
       <c r="G94">
-        <v>-0.2923130784831674</v>
+        <v>-3.963173135668824</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.03938707760839</v>
       </c>
       <c r="E95">
-        <v>-24.79031790637759</v>
+        <v>-27.97219582617908</v>
       </c>
       <c r="F95">
-        <v>-1.683073722785932</v>
+        <v>-0.5938708205603209</v>
       </c>
       <c r="G95">
-        <v>-0.1575992461386052</v>
+        <v>-2.836283528179369</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.716994416682166</v>
       </c>
       <c r="E96">
-        <v>-27.06121176700405</v>
+        <v>-29.34780131854109</v>
       </c>
       <c r="F96">
-        <v>-1.878411040040084</v>
+        <v>-0.8196738341546326</v>
       </c>
       <c r="G96">
-        <v>-0.2902032530204444</v>
+        <v>-3.371769043016068</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.37275630550909</v>
       </c>
       <c r="E97">
-        <v>-28.71406402353766</v>
+        <v>-32.7703970669313</v>
       </c>
       <c r="F97">
-        <v>-1.941426605105848</v>
+        <v>-1.15160810776302</v>
       </c>
       <c r="G97">
-        <v>-1.24295186990705</v>
+        <v>-4.321807370894573</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.99230567048841</v>
       </c>
       <c r="E98">
-        <v>-31.62527731613769</v>
+        <v>-34.23944309196758</v>
       </c>
       <c r="F98">
-        <v>-2.115215601110975</v>
+        <v>-0.8230013860116782</v>
       </c>
       <c r="G98">
-        <v>-0.8344791604148961</v>
+        <v>-5.304946661864754</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.55250158699171</v>
       </c>
       <c r="E99">
-        <v>-34.25111976219636</v>
+        <v>-36.87990118788601</v>
       </c>
       <c r="F99">
-        <v>-2.265165011630936</v>
+        <v>-1.096835626722513</v>
       </c>
       <c r="G99">
-        <v>-1.214756333046741</v>
+        <v>-4.719445486797439</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.04567408739582</v>
       </c>
       <c r="E100">
-        <v>-36.06943340202223</v>
+        <v>-39.06016896243396</v>
       </c>
       <c r="F100">
-        <v>-2.607405004097552</v>
+        <v>-1.239398485111711</v>
       </c>
       <c r="G100">
-        <v>-2.490377151382707</v>
+        <v>-4.545435745056968</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.44982729294993</v>
       </c>
       <c r="E101">
-        <v>-38.30763168031331</v>
+        <v>-41.15537614545883</v>
       </c>
       <c r="F101">
-        <v>-2.9297111633832</v>
+        <v>-1.533729848837418</v>
       </c>
       <c r="G101">
-        <v>-1.821844664753643</v>
+        <v>-5.648726807090896</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.76706391500849</v>
       </c>
       <c r="E102">
-        <v>-39.39138381559197</v>
+        <v>-44.3930946782489</v>
       </c>
       <c r="F102">
-        <v>-2.815861175909839</v>
+        <v>-2.05518215869529</v>
       </c>
       <c r="G102">
-        <v>-2.747913669140404</v>
+        <v>-4.534466621383744</v>
       </c>
     </row>
   </sheetData>
